--- a/branches/feat/jardin-datenpunkte/ValueSet-mii-vs-seltene-penetrance.xlsx
+++ b/branches/feat/jardin-datenpunkte/ValueSet-mii-vs-seltene-penetrance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T19:54:19+00:00</t>
+    <t>2026-09-01T20:22:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feat/jardin-datenpunkte/ValueSet-mii-vs-seltene-penetrance.xlsx
+++ b/branches/feat/jardin-datenpunkte/ValueSet-mii-vs-seltene-penetrance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T20:22:52+00:00</t>
+    <t>2026-09-01T21:17:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feat/jardin-datenpunkte/ValueSet-mii-vs-seltene-penetrance.xlsx
+++ b/branches/feat/jardin-datenpunkte/ValueSet-mii-vs-seltene-penetrance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T21:17:23+00:00</t>
+    <t>2026-09-01T21:34:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feat/jardin-datenpunkte/ValueSet-mii-vs-seltene-penetrance.xlsx
+++ b/branches/feat/jardin-datenpunkte/ValueSet-mii-vs-seltene-penetrance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T21:34:57+00:00</t>
+    <t>2026-09-01T21:46:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feat/jardin-datenpunkte/ValueSet-mii-vs-seltene-penetrance.xlsx
+++ b/branches/feat/jardin-datenpunkte/ValueSet-mii-vs-seltene-penetrance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T21:46:35+00:00</t>
+    <t>2026-09-02T02:40:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feat/jardin-datenpunkte/ValueSet-mii-vs-seltene-penetrance.xlsx
+++ b/branches/feat/jardin-datenpunkte/ValueSet-mii-vs-seltene-penetrance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T02:40:35+00:00</t>
+    <t>2026-09-02T02:52:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
